--- a/storage/app/public/vocabs/testbeds/1.3/testbeds_1-3.xlsx
+++ b/storage/app/public/vocabs/testbeds/1.3/testbeds_1-3.xlsx
@@ -98,7 +98,7 @@
     <t>Geothermal Project on TU Delft campus</t>
   </si>
   <si>
-    <t>#tu delft campus geothermal well#delft subsurface urban energy laboratory#(dsuel)#geothermal research project on tu delft#geothermal project at tu delft#geothermal research project at tu delft#dapgeo-01#dapgeo-02#dapgeo-03#dapgeo-04#dapgeo-05#geothermal delft#dapwell</t>
+    <t>#tu delft campus geothermal well#delft subsurface urban energy laboratory#(dsuel)#geothermal research project on tu delft#geothermal project at tu delft#geothermal research project at tu delft#dapgeo-01#dapgeo-02#dapgeo-03#dapgeo-04#dapgeo-05#geothermal delft#dapwell#tu delft campus geothermal project#geothermie delft#geothermal project on tu delft campus#del-gt-01#del-gt-02#del-gt-02-s1#del-gt-02-s2</t>
   </si>
   <si>
     <t>https://epos-msl.uu.nl/voc/testbeds/1.3/facility_names-geothermal_project_on_tu_delft_campus</t>
@@ -107,7 +107,7 @@
     <t>UK Geos</t>
   </si>
   <si>
-    <t>#uk geoenergy observatory#glasgow observatory#cheshire observatory</t>
+    <t>#uk geoenergy observatory#glasgow observatory#cheshire observatory#uk geoenergy observatories#ukgeos#glasgow observatories#cheshire observatories</t>
   </si>
   <si>
     <t>https://epos-msl.uu.nl/voc/testbeds/1.3/facility_names-uk_geos</t>
